--- a/buildplan_generator/output/25-099 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-099 GENERATED BUILD PLAN.xlsx
@@ -74,14 +74,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-053, 24-007, 25-096, 25-097, 25-036</t>
+          <t>25-036, 25-034, 25-035, 25-017, 25-016</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,15 @@
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -673,12 +671,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -722,8 +720,8 @@
       <c r="E9" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>3</v>
+      <c r="F9" s="9" t="n">
+        <v>1.2</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -732,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.5</t>
+          <t>ratio=1.17 (0.50-1.20)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -759,8 +757,8 @@
       <c r="E10" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>7.5</v>
+      <c r="F10" s="9" t="n">
+        <v>3.1</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -769,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>4.0-14.0</t>
+          <t>ratio=1.54 (0.20-2.33)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -813,8 +811,8 @@
       <c r="E12" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>9.199999999999999</v>
+      <c r="F12" s="9" t="n">
+        <v>3.9</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -823,7 +821,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>6.0-15.5</t>
+          <t>ratio=1.30 (0.65-2.38)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -850,8 +848,8 @@
       <c r="E13" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="10" t="n">
-        <v>4</v>
+      <c r="F13" s="9" t="n">
+        <v>1.5</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -860,7 +858,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>4.0-6.5</t>
+          <t>ratio=0.75 (0.45-1.62)</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -904,8 +902,8 @@
       <c r="E15" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F15" s="9" t="n">
-        <v>16.5</v>
+      <c r="F15" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -914,7 +912,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>global:12.0-240.8</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -942,7 +940,7 @@
         <v>8</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>24</v>
+        <v>9.6</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -951,7 +949,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>24.0-24.0</t>
+          <t>ratio=1.20 (n=1)</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -996,12 +994,12 @@
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1028,8 +1026,8 @@
       <c r="E19" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="10" t="n">
-        <v>5</v>
+      <c r="F19" s="9" t="n">
+        <v>1.5</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1038,7 +1036,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>3.0-5.0</t>
+          <t>ratio=0.75 (0.42-1.12)</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1065,8 +1063,8 @@
       <c r="E20" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="10" t="n">
-        <v>3.8</v>
+      <c r="F20" s="9" t="n">
+        <v>5.2</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1075,7 +1073,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>3.5-12.0</t>
+          <t>ratio=0.88 (0.67-1.75)</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1117,17 +1115,15 @@
         </is>
       </c>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1171,17 +1167,17 @@
       <c r="E24" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="F24" s="11" t="n">
-        <v>2</v>
+      <c r="F24" s="9" t="n">
+        <v>26.7</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=0.67 (0.20-1.00)</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1208,7 +1204,7 @@
       <c r="E25" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -1218,7 +1214,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-7.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1245,7 +1241,7 @@
       <c r="E26" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="10" t="n">
         <v>2</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
@@ -1255,7 +1251,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-16.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1299,8 +1295,8 @@
       <c r="E28" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F28" s="9" t="n">
-        <v>5.2</v>
+      <c r="F28" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1309,7 +1305,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>global:3.0-20.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1336,8 +1332,8 @@
       <c r="E29" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F29" s="9" t="n">
-        <v>68.8</v>
+      <c r="F29" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1346,7 +1342,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>global:10.0-120.8</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1390,8 +1386,8 @@
       <c r="E31" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F31" s="9" t="n">
-        <v>17</v>
+      <c r="F31" s="10" t="n">
+        <v>17.5</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1400,7 +1396,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>global:4.0-56.5</t>
+          <t>wc_ratio=1.17</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1425,17 +1421,15 @@
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
-      <c r="F32" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1462,17 +1456,17 @@
       <c r="E33" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="11" t="n">
-        <v>1.5</v>
+      <c r="F33" s="9" t="n">
+        <v>3.5</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.75 (1.50-5.00)</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1516,8 +1510,8 @@
       <c r="E35" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="10" t="n">
-        <v>6</v>
+      <c r="F35" s="9" t="n">
+        <v>3.5</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1526,7 +1520,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>5.0-14.0</t>
+          <t>ratio=1.17 (0.81-2.29)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1553,8 +1547,8 @@
       <c r="E36" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F36" s="10" t="n">
-        <v>9</v>
+      <c r="F36" s="9" t="n">
+        <v>4.5</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
@@ -1563,7 +1557,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>7.5-34.0</t>
+          <t>ratio=1.12 (0.71-1.96)</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1605,17 +1599,15 @@
         </is>
       </c>
       <c r="E38" s="8" t="n"/>
-      <c r="F38" s="11" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>4.5-4.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1659,8 +1651,8 @@
       <c r="E40" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="10" t="n">
-        <v>3.5</v>
+      <c r="F40" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1669,7 +1661,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>1.5-5.0</t>
+          <t>ratio=2.00 (0.50-2.50)</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1696,8 +1688,8 @@
       <c r="E41" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F41" s="9" t="n">
-        <v>5</v>
+      <c r="F41" s="10" t="n">
+        <v>6.4</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1706,7 +1698,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-8.0</t>
+          <t>wc_ratio=1.28</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1734,12 +1726,12 @@
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1767,12 +1759,12 @@
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1799,8 +1791,8 @@
       <c r="E44" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F44" s="10" t="n">
-        <v>5</v>
+      <c r="F44" s="9" t="n">
+        <v>10.1</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1809,7 +1801,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>4.0-8.5</t>
+          <t>ratio=1.27 (0.75-1.40)</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1837,12 +1829,12 @@
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1886,8 +1878,8 @@
       <c r="E47" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F47" s="10" t="n">
-        <v>5.8</v>
+      <c r="F47" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1896,7 +1888,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>3.0-8.0</t>
+          <t>ratio=3.00 (2.00-5.00)</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -1924,12 +1916,12 @@
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -1956,8 +1948,8 @@
       <c r="E49" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F49" s="10" t="n">
-        <v>2.5</v>
+      <c r="F49" s="9" t="n">
+        <v>4.5</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
@@ -1966,7 +1958,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.50 (0.83-5.00)</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -1980,7 +1972,7 @@
         </is>
       </c>
       <c r="F51" s="1" t="n">
-        <v>214.8</v>
+        <v>139.7</v>
       </c>
     </row>
   </sheetData>
@@ -2048,7 +2040,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-053, 24-007, 25-096, 25-097, 25-036</t>
+          <t>25-036, 25-034, 25-035, 25-017, 25-016</t>
         </is>
       </c>
     </row>
@@ -3201,35 +3193,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25-053</t>
+          <t>25-036</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24-007</t>
+          <t>25-034</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-096</t>
+          <t>25-035</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-097</t>
+          <t>25-017</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-036</t>
+          <t>25-016</t>
         </is>
       </c>
     </row>
@@ -3284,23 +3276,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3318,19 +3306,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>24-007, 25-036, 25-053, 25-096, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3344,7 +3328,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3353,12 +3337,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.0-3.5</t>
+          <t>ratio=1.17 (0.50-1.20)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-053, 25-036, 24-007</t>
+          <t>25-036, 25-035, 25-034</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3358,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.5</v>
+        <v>3.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3383,12 +3367,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4.0-14.0</t>
+          <t>ratio=1.54 (0.20-2.33)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-036, 24-007</t>
+          <t>25-036, 25-035, 25-034, 25-017, 25-016</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3388,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3413,12 +3397,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6.0-15.5</t>
+          <t>ratio=1.30 (0.65-2.38)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-053, 25-036</t>
+          <t>25-036, 25-035, 25-034, 25-017, 25-016</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3418,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3443,12 +3427,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4.0-6.5</t>
+          <t>ratio=0.75 (0.45-1.62)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-053, 25-036</t>
+          <t>25-036, 25-034, 25-017, 25-016</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3448,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3473,12 +3457,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>global:12.0-240.8</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3478,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>9.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3503,12 +3487,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>24.0-24.0</t>
+          <t>ratio=1.20 (n=1)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-053</t>
+          <t>25-034</t>
         </is>
       </c>
     </row>
@@ -3528,19 +3512,15 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>25-036, 25-053, 25-096, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3554,7 +3534,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3563,12 +3543,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3.0-5.0</t>
+          <t>ratio=0.75 (0.42-1.12)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-053, 25-036</t>
+          <t>25-036, 25-035, 25-017, 25-016</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3564,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3593,12 +3573,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3.5-12.0</t>
+          <t>ratio=0.88 (0.67-1.75)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-053, 25-036</t>
+          <t>25-036, 25-035, 25-034, 25-017, 25-016</t>
         </is>
       </c>
     </row>
@@ -3614,21 +3594,21 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>26.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=0.67 (0.20-1.00)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-036</t>
+          <t>25-036, 25-035, 25-034, 25-017, 25-016</t>
         </is>
       </c>
     </row>
@@ -3644,23 +3624,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3683,12 +3659,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>global:0.5-7.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -3713,12 +3689,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>global:0.5-16.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3710,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3743,12 +3719,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>global:3.0-20.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3740,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>68.8</v>
+        <v>10</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3773,12 +3749,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>global:10.0-120.8</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3770,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3803,12 +3779,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>global:4.0-56.5</t>
+          <t>wc_ratio=1.17</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -3824,23 +3800,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3854,21 +3826,21 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.75 (1.50-5.00)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-036</t>
+          <t>25-036, 25-034, 25-017, 25-016</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3856,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3893,12 +3865,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5.0-14.0</t>
+          <t>ratio=1.17 (0.81-2.29)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-053, 25-036, 24-007</t>
+          <t>25-036, 25-035, 25-034, 25-017, 25-016</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3886,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3923,12 +3895,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>7.5-34.0</t>
+          <t>ratio=1.12 (0.71-1.96)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-053, 25-036, 24-007</t>
+          <t>25-036, 25-035, 25-034, 25-017, 25-016</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3916,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3953,12 +3925,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>global:1.0-8.0</t>
+          <t>wc_ratio=1.28</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -3974,23 +3946,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4.5-4.5</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>25-097, 25-096, 25-053, 25-036, 24-007</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4004,7 +3972,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4013,12 +3981,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.5-5.0</t>
+          <t>ratio=2.00 (0.50-2.50)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-053, 25-036, 24-007</t>
+          <t>25-036, 25-035, 25-034, 25-017, 25-016</t>
         </is>
       </c>
     </row>
@@ -4038,19 +4006,15 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>24-007, 25-036, 25-053, 25-096, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4068,19 +4032,15 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>24-007, 25-053, 25-096, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4094,7 +4054,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>10.1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4103,12 +4063,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4.0-8.5</t>
+          <t>ratio=1.27 (0.75-1.40)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-053, 25-036</t>
+          <t>25-036, 25-035, 25-034, 25-017, 25-016</t>
         </is>
       </c>
     </row>
@@ -4128,19 +4088,15 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>25-036, 25-053, 25-096, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4154,7 +4110,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4163,12 +4119,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3.0-8.0</t>
+          <t>ratio=3.00 (2.00-5.00)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-036, 24-007</t>
+          <t>25-036, 25-035, 25-034, 25-016</t>
         </is>
       </c>
     </row>
@@ -4188,19 +4144,15 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>24-007, 25-036, 25-053, 25-096, 25-097</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4214,7 +4166,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4223,12 +4175,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.50 (0.83-5.00)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-053, 25-036, 24-007</t>
+          <t>25-035, 25-034, 25-017, 25-016</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-099 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-099 GENERATED BUILD PLAN.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -84,12 +84,6 @@
         <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -109,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,7 +117,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-035, 25-017, 25-016</t>
+          <t>25-034, 25-036, 25-035, 25-017, 25-016</t>
         </is>
       </c>
     </row>
@@ -638,12 +631,12 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -671,12 +664,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -721,7 +714,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -730,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.50-1.20)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -758,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.54 (0.20-2.33)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -812,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>3.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -821,7 +814,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.30 (0.65-2.38)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -849,7 +842,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -858,7 +851,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.45-1.62)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -902,17 +895,17 @@
       <c r="E15" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>12</v>
+      <c r="F15" s="9" t="n">
+        <v>2.7</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -939,17 +932,17 @@
       <c r="E16" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F16" s="11" t="n">
-        <v>9.6</v>
+      <c r="F16" s="9" t="n">
+        <v>5.1</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.20 (n=1)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -994,12 +987,12 @@
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1027,7 +1020,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1036,7 +1029,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.42-1.12)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1064,7 +1057,7 @@
         <v>6</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1073,7 +1066,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.67-1.75)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1118,12 +1111,12 @@
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1168,7 +1161,7 @@
         <v>40</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>26.7</v>
+        <v>8.4</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1177,7 +1170,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.67 (0.20-1.00)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1204,17 +1197,17 @@
       <c r="E25" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="10" t="n">
-        <v>1</v>
+      <c r="F25" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1241,17 +1234,17 @@
       <c r="E26" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F26" s="10" t="n">
-        <v>2</v>
+      <c r="F26" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1300,12 +1293,12 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1337,12 +1330,12 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1386,17 +1379,17 @@
       <c r="E31" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F31" s="10" t="n">
-        <v>17.5</v>
+      <c r="F31" s="9" t="n">
+        <v>20.9</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.17</t>
+          <t>group_total:21h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1424,12 +1417,12 @@
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1456,17 +1449,17 @@
       <c r="E33" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="9" t="n">
-        <v>3.5</v>
+      <c r="F33" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.75 (1.50-5.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1511,7 +1504,7 @@
         <v>3</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1520,7 +1513,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.81-2.29)</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1548,7 +1541,7 @@
         <v>4</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>4.5</v>
+        <v>15.9</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
@@ -1557,7 +1550,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.12 (0.71-1.96)</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1602,12 +1595,12 @@
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1652,7 +1645,7 @@
         <v>2</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1661,7 +1654,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.00 (0.50-2.50)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1688,17 +1681,17 @@
       <c r="E41" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F41" s="10" t="n">
-        <v>6.4</v>
+      <c r="F41" s="9" t="n">
+        <v>0.1</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.28</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1726,12 +1719,12 @@
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1759,12 +1752,12 @@
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1792,7 +1785,7 @@
         <v>8</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>10.1</v>
+        <v>11.7</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1801,7 +1794,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.27 (0.75-1.40)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1829,12 +1822,12 @@
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1879,7 +1872,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1888,7 +1881,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.00 (2.00-5.00)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -1916,12 +1909,12 @@
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -1949,7 +1942,7 @@
         <v>3</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
@@ -1958,7 +1951,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.83-5.00)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -1972,7 +1965,7 @@
         </is>
       </c>
       <c r="F51" s="1" t="n">
-        <v>139.7</v>
+        <v>128.7</v>
       </c>
     </row>
   </sheetData>
@@ -2040,7 +2033,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-035, 25-017, 25-016</t>
+          <t>25-034, 25-036, 25-035, 25-017, 25-016</t>
         </is>
       </c>
     </row>
@@ -3193,14 +3186,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25-036</t>
+          <t>25-034</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-034</t>
+          <t>25-036</t>
         </is>
       </c>
     </row>
@@ -3280,15 +3273,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3306,15 +3303,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3328,7 +3329,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3337,12 +3338,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.50-1.20)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-036, 25-035, 25-034</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3359,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3367,12 +3368,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=1.54 (0.20-2.33)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-036, 25-035, 25-034, 25-017, 25-016</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3389,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3397,12 +3398,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=1.30 (0.65-2.38)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-036, 25-035, 25-034, 25-017, 25-016</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3419,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3427,12 +3428,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.45-1.62)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-017, 25-016</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -3448,21 +3449,21 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>2.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -3478,21 +3479,21 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.20 (n=1)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-034</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -3512,15 +3513,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3534,7 +3539,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3543,12 +3548,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.42-1.12)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-036, 25-035, 25-017, 25-016</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3569,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3573,12 +3578,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.67-1.75)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-036, 25-035, 25-034, 25-017, 25-016</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3599,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.7</v>
+        <v>8.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3603,12 +3608,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ratio=0.67 (0.20-1.00)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-036, 25-035, 25-034, 25-017, 25-016</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -3628,15 +3633,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3650,21 +3659,21 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -3680,21 +3689,21 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -3714,17 +3723,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -3744,17 +3753,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -3770,21 +3779,21 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17.5</v>
+        <v>20.9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>wc_ratio=1.17</t>
+          <t>group_total:21h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -3804,15 +3813,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3826,21 +3839,21 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ratio=1.75 (1.50-5.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-017, 25-016</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3869,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3865,12 +3878,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.81-2.29)</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-036, 25-035, 25-034, 25-017, 25-016</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3899,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4.5</v>
+        <v>15.9</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3895,12 +3908,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=1.12 (0.71-1.96)</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-036, 25-035, 25-034, 25-017, 25-016</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -3916,21 +3929,21 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6.4</v>
+        <v>0.1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>wc_ratio=1.28</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -3950,15 +3963,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3972,7 +3989,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3981,12 +3998,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ratio=2.00 (0.50-2.50)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-036, 25-035, 25-034, 25-017, 25-016</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4006,15 +4023,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4032,15 +4053,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4054,7 +4079,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>10.1</v>
+        <v>11.7</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4063,12 +4088,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ratio=1.27 (0.75-1.40)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-036, 25-035, 25-034, 25-017, 25-016</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4088,15 +4113,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4110,7 +4139,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4119,12 +4148,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ratio=3.00 (2.00-5.00)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-036, 25-035, 25-034, 25-016</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4144,15 +4173,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4166,7 +4199,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4175,12 +4208,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.83-5.00)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-035, 25-034, 25-017, 25-016</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-099 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-099 GENERATED BUILD PLAN.xlsx
@@ -714,7 +714,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -805,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>group_total:12h</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -842,7 +842,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>group_total:12h</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -896,7 +896,7 @@
         <v>12</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -933,7 +933,7 @@
         <v>8</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1020,7 +1020,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1057,7 +1057,7 @@
         <v>6</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1161,7 +1161,7 @@
         <v>40</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>8.4</v>
+        <v>13.2</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1198,7 +1198,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1235,7 +1235,7 @@
         <v>2</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1380,7 +1380,7 @@
         <v>15</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>3</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>group_total:24h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1541,7 +1541,7 @@
         <v>4</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>15.9</v>
+        <v>10.6</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>group_total:24h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1645,7 +1645,7 @@
         <v>2</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1785,7 +1785,7 @@
         <v>8</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>11.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1872,7 +1872,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -1942,7 +1942,7 @@
         <v>3</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="F51" s="1" t="n">
-        <v>128.7</v>
+        <v>119.4</v>
       </c>
     </row>
   </sheetData>
@@ -3329,7 +3329,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9.800000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>group_total:12h</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>group_total:12h</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8.4</v>
+        <v>13.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>group_total:24h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>15.9</v>
+        <v>10.6</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>group_total:24h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>11.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
